--- a/artfynd/A 7097-2025 artfynd.xlsx
+++ b/artfynd/A 7097-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369540</v>
+        <v>122369538</v>
       </c>
       <c r="B4" t="n">
         <v>56593</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386859</v>
+        <v>386858</v>
       </c>
       <c r="R4" t="n">
-        <v>6648452</v>
+        <v>6648447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122369538</v>
+        <v>122369539</v>
       </c>
       <c r="B5" t="n">
         <v>56593</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386858</v>
+        <v>386865</v>
       </c>
       <c r="R5" t="n">
-        <v>6648447</v>
+        <v>6648401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369539</v>
+        <v>122369536</v>
       </c>
       <c r="B6" t="n">
         <v>56593</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386865</v>
+        <v>386834</v>
       </c>
       <c r="R6" t="n">
-        <v>6648401</v>
+        <v>6648472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>På häll.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122369536</v>
+        <v>122369540</v>
       </c>
       <c r="B7" t="n">
         <v>56593</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386834</v>
+        <v>386859</v>
       </c>
       <c r="R7" t="n">
-        <v>6648472</v>
+        <v>6648452</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På häll.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7097-2025 artfynd.xlsx
+++ b/artfynd/A 7097-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369541</v>
+        <v>122369540</v>
       </c>
       <c r="B3" t="n">
         <v>56593</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386794</v>
+        <v>386859</v>
       </c>
       <c r="R3" t="n">
-        <v>6648465</v>
+        <v>6648452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369538</v>
+        <v>122369536</v>
       </c>
       <c r="B4" t="n">
         <v>56593</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386858</v>
+        <v>386834</v>
       </c>
       <c r="R4" t="n">
-        <v>6648447</v>
+        <v>6648472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>På häll.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122369539</v>
+        <v>122369541</v>
       </c>
       <c r="B5" t="n">
         <v>56593</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386865</v>
+        <v>386794</v>
       </c>
       <c r="R5" t="n">
-        <v>6648401</v>
+        <v>6648465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369536</v>
+        <v>122369538</v>
       </c>
       <c r="B6" t="n">
         <v>56593</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386834</v>
+        <v>386858</v>
       </c>
       <c r="R6" t="n">
-        <v>6648472</v>
+        <v>6648447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På häll.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122369540</v>
+        <v>122369539</v>
       </c>
       <c r="B7" t="n">
         <v>56593</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386859</v>
+        <v>386865</v>
       </c>
       <c r="R7" t="n">
-        <v>6648452</v>
+        <v>6648401</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7097-2025 artfynd.xlsx
+++ b/artfynd/A 7097-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369540</v>
+        <v>122369539</v>
       </c>
       <c r="B3" t="n">
         <v>56593</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386859</v>
+        <v>386865</v>
       </c>
       <c r="R3" t="n">
-        <v>6648452</v>
+        <v>6648401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369536</v>
+        <v>122369541</v>
       </c>
       <c r="B4" t="n">
         <v>56593</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386834</v>
+        <v>386794</v>
       </c>
       <c r="R4" t="n">
-        <v>6648472</v>
+        <v>6648465</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På häll.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122369541</v>
+        <v>122369536</v>
       </c>
       <c r="B5" t="n">
         <v>56593</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386794</v>
+        <v>386834</v>
       </c>
       <c r="R5" t="n">
-        <v>6648465</v>
+        <v>6648472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>På häll.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122369539</v>
+        <v>122369540</v>
       </c>
       <c r="B7" t="n">
         <v>56593</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386865</v>
+        <v>386859</v>
       </c>
       <c r="R7" t="n">
-        <v>6648401</v>
+        <v>6648452</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7097-2025 artfynd.xlsx
+++ b/artfynd/A 7097-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369539</v>
+        <v>122369536</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386865</v>
+        <v>386834</v>
       </c>
       <c r="R3" t="n">
-        <v>6648401</v>
+        <v>6648472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>På häll.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369541</v>
+        <v>122369540</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386794</v>
+        <v>386859</v>
       </c>
       <c r="R4" t="n">
-        <v>6648465</v>
+        <v>6648452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122369536</v>
+        <v>122369541</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386834</v>
+        <v>386794</v>
       </c>
       <c r="R5" t="n">
-        <v>6648472</v>
+        <v>6648465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På häll.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
         <v>122369538</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122369540</v>
+        <v>122369539</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386859</v>
+        <v>386865</v>
       </c>
       <c r="R7" t="n">
-        <v>6648452</v>
+        <v>6648401</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7097-2025 artfynd.xlsx
+++ b/artfynd/A 7097-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369536</v>
+        <v>122369538</v>
       </c>
       <c r="B3" t="n">
         <v>56594</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386834</v>
+        <v>386858</v>
       </c>
       <c r="R3" t="n">
-        <v>6648472</v>
+        <v>6648447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På häll.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369540</v>
+        <v>122369539</v>
       </c>
       <c r="B4" t="n">
         <v>56594</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386859</v>
+        <v>386865</v>
       </c>
       <c r="R4" t="n">
-        <v>6648452</v>
+        <v>6648401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369538</v>
+        <v>122369540</v>
       </c>
       <c r="B6" t="n">
         <v>56594</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386858</v>
+        <v>386859</v>
       </c>
       <c r="R6" t="n">
-        <v>6648447</v>
+        <v>6648452</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122369539</v>
+        <v>122369536</v>
       </c>
       <c r="B7" t="n">
         <v>56594</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386865</v>
+        <v>386834</v>
       </c>
       <c r="R7" t="n">
-        <v>6648401</v>
+        <v>6648472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>På häll.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7097-2025 artfynd.xlsx
+++ b/artfynd/A 7097-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369538</v>
+        <v>122369540</v>
       </c>
       <c r="B3" t="n">
         <v>56594</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386858</v>
+        <v>386859</v>
       </c>
       <c r="R3" t="n">
-        <v>6648447</v>
+        <v>6648452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122369539</v>
+        <v>122369536</v>
       </c>
       <c r="B4" t="n">
         <v>56594</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386865</v>
+        <v>386834</v>
       </c>
       <c r="R4" t="n">
-        <v>6648401</v>
+        <v>6648472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka.</t>
+          <t>På häll.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122369541</v>
+        <v>122369538</v>
       </c>
       <c r="B5" t="n">
         <v>56594</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386794</v>
+        <v>386858</v>
       </c>
       <c r="R5" t="n">
-        <v>6648465</v>
+        <v>6648447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122369540</v>
+        <v>122369539</v>
       </c>
       <c r="B6" t="n">
         <v>56594</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386859</v>
+        <v>386865</v>
       </c>
       <c r="R6" t="n">
-        <v>6648452</v>
+        <v>6648401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt under betad tall.</t>
+          <t>Enstaka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122369536</v>
+        <v>122369541</v>
       </c>
       <c r="B7" t="n">
         <v>56594</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386834</v>
+        <v>386794</v>
       </c>
       <c r="R7" t="n">
-        <v>6648472</v>
+        <v>6648465</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På häll.</t>
+          <t>Rikligt under betad tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7097-2025 artfynd.xlsx
+++ b/artfynd/A 7097-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73282241</v>
+        <v>78279666</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horntjärnsmyren, Vrm</t>
+          <t>Gyltamossarna, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386815.8978497714</v>
+        <v>386853</v>
       </c>
       <c r="R2" t="n">
-        <v>6648388.86645118</v>
+        <v>6648346</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,76 +766,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122369540</v>
+        <v>73282241</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnhöjden Värmland, Vrm</t>
+          <t>Horntjärnsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386859</v>
+        <v>386816</v>
       </c>
       <c r="R3" t="n">
-        <v>6648452</v>
+        <v>6648389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,17 +850,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2018-09-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt under betad tall.</t>
+          <t>2018-09-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,12 +880,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alessandra Munari</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Måreby</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -905,12 +895,7 @@
         <v>122369536</v>
       </c>
       <c r="B4" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,12 +1005,7 @@
         <v>122369538</v>
       </c>
       <c r="B5" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,12 +1115,7 @@
         <v>122369539</v>
       </c>
       <c r="B6" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,15 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122369541</v>
+        <v>122369540</v>
       </c>
       <c r="B7" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386794</v>
+        <v>386859</v>
       </c>
       <c r="R7" t="n">
-        <v>6648465</v>
+        <v>6648452</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,6 +1329,222 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122369541</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnhöjden Värmland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>386794</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6648465</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt under betad tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97748952</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>O om Västra Gyltamossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>386706</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6648416</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
